--- a/data/개발현황.xlsx
+++ b/data/개발현황.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="개발 현황 요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="기능 전체 목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="일일 개발 현황" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="커밋 이력" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발 현황 요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능 전체 목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일 개발 현황" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커밋 이력" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 04-24 (15일)</t>
+          <t>2026-04-10 ~ 04-27 (18일)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>122건</t>
+          <t>184건</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>17 / 26개 (65%)</t>
+          <t>20 / 29개 (69%)</t>
         </is>
       </c>
     </row>
@@ -700,29 +700,53 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24  ■■■■  (9)</t>
+          <t>2026-04-24  ■■■■■■■■■■■  (22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-25  ■■■■■  (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-26  ■■■■■■■■■■■■  (25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27  ■■■■■■  (13)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A18:E18"/>
+  <mergeCells count="21">
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="B6:E6"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -735,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -892,9 +916,36 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25 ~ 04-27</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>운영 품질 개선</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>입출고 단계형 Wizard UX·BOM Where-Used
+코드 품질 대정비(Phase 5)·CI 도입
+로그인 화면 구현·ERP 카테고리 코드 정비</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -911,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1147,12 +1198,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>직원 명단 관리</t>
+          <t>BOM Where-Used 조회</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1168,7 +1219,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>부서별 담당 색상 배지 표시</t>
+          <t>직원 명단 관리</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1189,12 +1240,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>관리자 화면</t>
+          <t>부서별 담당 색상 배지 표시</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1210,7 +1261,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>데이터 CSV 내보내기</t>
+          <t>관리자 화면</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1231,12 +1282,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>PC 화면 (데스크톱)</t>
+          <t>데이터 CSV 내보내기</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1252,7 +1303,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>모바일 화면</t>
+          <t>PC 화면 (데스크톱)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1273,7 +1324,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>다크 / 라이트 모드</t>
+          <t>모바일 화면</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1294,87 +1345,83 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
+          <t>다크 / 라이트 모드</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>입출고 단계형 Wizard UX</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
           <t>원클릭 실행 (start.bat)</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>생산 / 분해 / 반품 처리 Queue</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr"/>
+      <c r="E20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>QR · 바코드 스캔 완성</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>입출고</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>모바일 카메라 연동</t>
-        </is>
-      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>테스트 자동화 (CI)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n">
@@ -1382,12 +1429,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>실제 운영 데이터 입력</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -1395,11 +1442,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>권동환 사원 협의 후</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
@@ -1407,12 +1450,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>로그인 및 권한 관리</t>
+          <t>생산 / 분해 / 반품 처리 Queue</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -1428,12 +1471,12 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>QR · 바코드 스캔 완성</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -1443,7 +1486,7 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버</t>
+          <t>모바일 카메라 연동</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1496,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>실제 운영 데이터 입력</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -1466,7 +1509,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>권동환 사원 협의 후</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
@@ -1474,12 +1521,12 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>로그인 및 권한 관리</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -1487,7 +1534,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr"/>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>화면 구현 완료 — 인증 연동 예정</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
@@ -1495,20 +1546,87 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
           <t>부서별 진행현황 화면</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>사장님 요청 — 검토 중</t>
         </is>
@@ -1525,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1817,7 +1935,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -1829,6 +1947,78 @@
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 탭 좌:작업설정+실행 / 우:(품목테이블+수량row) 3영역 재배
+2026-04-25 desktop: 입출고 내역 필터 단순화 — 검색/기간/유형만 기본 노출
+2026-04-25 desktop: 입출고 탭 단계형 wizard 재구성
+2026-04-25 desktop: 입출고 wizard UX 보정 — 안내문 정리·확인 팝업·자동 스크롤·상
+2026-04-25 desktop: 입출고 wizard UX 마감 보정 — 초기 locked 카드 숨김·st</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: 에러 응답 표준화 + 전역 예외/로그 회전
+2026-04-26 backend: BOM where-used (read-only) API 추가
+2026-04-26 refactor: inventory 라우터 패키지 분할
+2026-04-26 backend: get_item 단건 경로도 bulk_compute 사용
+2026-04-26 frontend: _warehouse_steps.tsx 1135줄 파일 분할</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 refactor: Phase 5.5 — 8개 영역 A− → A 진입 (보안 제외)
+2026-04-27 refactor: Phase 5.6 — 외부 리뷰 P2 반영 + 잔여 A− → A
+2026-04-27 refactor: BA→AA 전면 교체 + BF 잔재 완전 제거
+2026-04-27 refactor: BA→AA 잔존 6파일 수정 + migrate 스크립트 경로 이동
+2026-04-27 fix: CI 백엔드 테스트 통과 — CategoryEnum.BA 잔존 3건 → AA</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
@@ -1845,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4560,6 +4750,1370 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>1d2ed77</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-24 refactor: main에서 vault/ 폴더 제거 (vault-sync로 이동)</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>32a472e</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24 docs: define vault branch policy</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>eb96258</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-24 docs: 개발 현황 및 재고 매칭 데이터 업데이트</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>e2abfec</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24 admin: AdminView UX 개선 + 이력 화면 정리</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>e0629bf</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-24 admin: 바코드 스캐너 개선 + 모바일 스캔 테스트 문서 추가</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>34ee2b6</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24 refactor: vault/ 제거 (vault-sync 브랜치로 분리)</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>c4a51bb</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>Merge branch 'refactor/admin-ux'</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>38f3eab</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'main' of https://github.com/Hw-03/ERP</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>c8f2361</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-24 desktop: 전면 UX/UI 개선 — KPI·CSS버그·필터·위험영역·알림뱃지</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>d1ffeef</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24 devx: start.bat 다중 PC 대응 + Python 3.13 호환</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>2108c0c</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>refactor: 데스크톱 재고 KPI 세분화 + 조치필요 카드 분리</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>refactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>03955e0</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24 desktop: 입출고 탭 시각 위계 재정비</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>33e200d</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-24 devx: 프론트 dev 서버 배너 커스터마이징</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>5426b57</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 탭 좌:작업설정+실행 / 우:(품목테이블+수량row) 3영역 재배치</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>9d76360</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 내역 필터 단순화 — 검색/기간/유형만 기본 노출</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>16386b5</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 탭 단계형 wizard 재구성</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>f2e6fd5</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 wizard UX 보정 — 안내문 정리·확인 팝업·자동 스크롤·상단 status pill</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>c0b4be0</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 wizard UX 마감 보정 — 초기 locked 카드 숨김·sticky 카드형·스크롤 여유</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>3908370</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 입출고 부분 실패 안전 처리 — 결과 모달·자동 refresh·로드 실패 안내</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>be1a13e</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 desktop: 공용 UI 부품 6종 추출 + 입출고 UX 마감</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>6b60514</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 docs: 운영 매뉴얼·구조 문서·보류 설계서·운영 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>2e30fda</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 refactor: useWarehouseFilters hook 추출 — DesktopWarehouseView 필터 로직 분리</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>5d9ba50</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-25 refactor: useWarehouseWizardState + useWarehouseCompletionFeedback hook 추출</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>eefd11e</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25 refactor: Phase 3 대형 구조 정리 — 4개 Desktop View + 백엔드 helper</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>dd3d3eb</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: 에러 응답 표준화 + 전역 예외/로그 회전</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>1df69e5</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: BOM where-used (read-only) API 추가</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>e6b6d08</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 refactor: inventory 라우터 패키지 분할</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>9c17981</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: get_item 단건 경로도 bulk_compute 사용</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>78d4b5c</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 frontend: _warehouse_steps.tsx 1135줄 파일 분할</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>cb089e8</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 frontend: ErrorBoundary + AdminBomContext + useResource</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>7813ddf</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 docs: GLOSSARY/ERD 신설 + Phase 4 결과 갱신 + reconcile 스크립트</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>3ba9a53</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: 모든 라우터 에러 응답 표준화 (http_error)</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>7f22b34</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: request_id middleware + OpenAPI 태그 보강 + CORS env wiring</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>585bc19</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 frontend: Admin 4섹션 Context 패턴 확장</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>607e95a</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 frontend: BOM Where-Used UI (관리자 BOM 우측 패널)</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>3a4108e</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 docs: README 허브 + Phase 5 결과 + plan 문서 갱신</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>415cf9f</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 docs: Phase 5 회귀 테스트 결과 + P1 회귀 1건 기록</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>ecb7307</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: root() version 하드코딩 제거 (app.version 참조)</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>634f346</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: 응답 모델 erp_code Optional 통일 (P1 회귀)</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>a39161c</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 backend: exception handler가 request.state.request_id 우선 사용</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>1359e23</t>
+        </is>
+      </c>
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 frontend: 거래 export URL 기본 30일 자동 부여 + 라벨 갱신</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>bf983fb</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>chore: ignore local verification artifacts</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>chore</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>9545ad3</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 refactor: scripts/ 목적별 3폴더 재배치 (ops/migrations/dev)</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>eb2fb91</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 docs: deep-research → docs/research/MOBILE_BARCODE_ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>3f4d2a2</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 docs: README 폴더 트리 섹션 + scripts/ops 경로 갱신</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>0861bab</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 fix: Phase 5.1 정합/성능/백업 — capacity·BOM N+1·WAL backup·erp_code 타입 정합</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>9b77054</t>
+        </is>
+      </c>
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 fix: Phase 5.2 — DB 보강·운영·프론트 성능·컴포넌트 분할 (4개 영역 A−)</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>9004359</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 fix: Phase 5.3 — API/UX/상태/테스트 4개 영역 A− 진입</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>cbafdf6</t>
+        </is>
+      </c>
+      <c r="C172" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-26 fix: Phase 5.4 — main.py 부작용 제거 + N+1 정리 + CI 도입</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>1a31d1b</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-26 refactor: Phase 5.5 — 8개 영역 A− → A 진입 (보안 제외)</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>f326059</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 refactor: Phase 5.6 — 외부 리뷰 P2 반영 + 잔여 A− → A</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>4ec3c42</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 refactor: BA→AA 전면 교체 + BF 잔재 완전 제거</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>6da59f6</t>
+        </is>
+      </c>
+      <c r="C176" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 refactor: BA→AA 잔존 6파일 수정 + migrate 스크립트 경로 이동</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>7495788</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 fix: CI 백엔드 테스트 통과 — CategoryEnum.BA 잔존 3건 → AA</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>6b2f5d4</t>
+        </is>
+      </c>
+      <c r="C178" s="17" t="inlineStr">
+        <is>
+          <t>Merge branch 'feat/merged' into main</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>4a8793a</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 desktop: 대시보드 헤더 정리 — 품절/부족 뱃지·생산가능 버튼 제거, 생산가능 패널을 즉시/최대 표기 + 클릭 시 상세 모달</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>2a327f4</t>
+        </is>
+      </c>
+      <c r="C180" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 docs: 기존 MES vs 현재 ERP 비교 분석 보고서 추가</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>edecb6b</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 refactor: Playwright MCP 서버 설정 추가 (.mcp.json)</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>64261ab</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 refactor: vault/ 전체를 .gitignore에 추가 (main 브랜치 vault-free 유지)</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>ce2083a</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 fix: 직원 is_active 버그 수정 + 관리자 확인 팝업 커스텀 UI 교체, docs/design 정리</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>d70b409</t>
+        </is>
+      </c>
+      <c r="C184" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 fix: 인코딩 깨짐·마이그레이션 스크립트 수정, 로그인 에셋 교체</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>5423ec9</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-27 feat: ERP 로그인 게이트 구현 (인트로 애니메이션 + 로그인 폼)</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/개발현황.xlsx
+++ b/data/개발현황.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 ERP 재고관리 시스템 개발 현황</t>
+          <t>📊 DEXCOWIN MES 개발 현황</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 04-27 (18일)</t>
+          <t>2026-04-10 ~ 04-30 (21일)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>184건</t>
+          <t>212건</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>20 / 29개 (69%)</t>
+          <t>23 / 33개 (70%)</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,34 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27  ■■■■■■  (13)</t>
+          <t>2026-04-27  ■■■■■■■  (14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28  ■■■■■■  (13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29  ■■■■■■  (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30  ■  (2)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="24">
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A11:E11"/>
@@ -734,10 +756,12 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A8:E8"/>
@@ -759,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -932,20 +956,47 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>운영 품질 개선</t>
+          <t>코드 품질 정비</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>입출고 단계형 Wizard UX·BOM Where-Used
+          <t>입출고 단계형 Wizard UX·BOM Where-Used 조회
 코드 품질 대정비(Phase 5)·CI 도입
-로그인 화면 구현·ERP 카테고리 코드 정비</t>
+로그인 화면 구현·카테고리 코드 정비</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28 ~ 04-30</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>현장 운영 투입</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>창고 승인 기반 입출고 흐름·직원별 장바구니
+작업자 PIN 로그인·감사 이력
+시스템명 MES 통일·품목 분류 개편(진행 중)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -962,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1424,69 +1475,77 @@
       <c r="E21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n">
+      <c r="A22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>창고 승인 기반 입출고 흐름</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>재고</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>요청→승인→처리 단계 분리</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>생산 / 분해 / 반품 처리 Queue</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>직원별 저장형 입출고 장바구니</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>화면 이탈 후에도 작업 유지</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>QR · 바코드 스캔 완성</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>입출고</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>모바일 카메라 연동</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>작업자 PIN 로그인 + 감사 이력</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>수정 이력 자동 기록</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1555,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>실제 운영 데이터 입력</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -1509,11 +1568,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>권동환 사원 협의 후</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
@@ -1521,12 +1576,12 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>로그인 및 권한 관리</t>
+          <t>생산 / 분해 / 반품 처리 Queue</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -1534,11 +1589,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>화면 구현 완료 — 인증 연동 예정</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
@@ -1546,12 +1597,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>QR · 바코드 스캔 완성</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -1561,7 +1612,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버</t>
+          <t>모바일 카메라 연동</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1622,12 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>실제 운영 데이터 입력</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
@@ -1584,7 +1635,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>권동환 사원 협의 후</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n">
@@ -1592,12 +1647,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>로그인 및 권한 관리</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -1605,7 +1660,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr"/>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>화면 구현 완료 — 인증 연동 예정</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n">
@@ -1613,22 +1672,114 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
           <t>부서별 진행현황 화면</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>품목 분류 개편 (process_type_code)</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2007,7 +2158,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
@@ -2021,6 +2172,75 @@
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 로그인 후 기본 탭을 대시보드로 고정
+2026-04-28 feat: 작업자 PIN 로그인 + 직원/거래 수정 감사 이력
+2026-04-28 fix: 거래 수량 보정 중복/예약재고 검증 보강
+2026-04-28 fix: 작업자 자동진입 검증 및 pending 방어 보강
+2026-04-28 docs: 주간보고·개발현황·검증 스크린샷 일괄 커밋</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 fix: 현장 운영 전 핵심 UX/승인 버그 수정
+2026-04-29 fix: MES 명칭 정리와 현장 UX 잔여 보완
+2026-04-29 refactor: X-Ray → DEXCOWIN 시스템명 교체 + MES 용어 정리 + 
+merge: fix/mes-terminology-field-ux-pass2 → main
+2026-04-29 desktop: 패널 슬라이드 애니메이션 GPU 가속 + 입출고 UX 개선</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor: 프론트 품목 분류를 process_type_code 기준으로 정리
+2026-04-29 refactor: DB 재생성(722건) + process_type_code 문서 단일화</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6114,6 +6334,622 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t>8401372</t>
+        </is>
+      </c>
+      <c r="C186" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-27 feat: 기본 테마 라이트 모드 전환, 로그인 게이트 항상 표시</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>643e96c</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 로그인 후 기본 탭을 대시보드로 고정</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t>f009903</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 feat: 작업자 PIN 로그인 + 직원/거래 수정 감사 이력</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>827d499</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 거래 수량 보정 중복/예약재고 검증 보강</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t>8cbcf73</t>
+        </is>
+      </c>
+      <c r="C190" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 작업자 자동진입 검증 및 pending 방어 보강</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>f080388</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 docs: 주간보고·개발현황·검증 스크린샷 일괄 커밋</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t>c947e02</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 feat: 창고 승인 기반 입출고 요청 흐름 구현</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>b9c25b5</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: start.bat에 --migrate 추가하여 신규 컬럼 자동 반영</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>847f0a7</t>
+        </is>
+      </c>
+      <c r="C194" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 입출고 요청 타입별 bucket 조합 검증 추가</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>d4c37d8</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 merge: feature/warehouse-approval-flow → main (창고 승인 기반 입출고 요청 흐름)</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>babded3</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 docs: 루트 PNG 27개를 regression 폴더로 정리</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>4b426f4</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 feat: 직원별 저장형 입출고 장바구니 구현</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="inlineStr">
+        <is>
+          <t>37e8917</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-28 merge: feature/erp-polish-phase1 → main (직원별 저장형 입출고 장바구니)</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>b9471b6</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-28 fix: 작업유형 변경 시 ghost draft 생성 방지</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
+          <t>f63d442</t>
+        </is>
+      </c>
+      <c r="C200" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 fix: 현장 운영 전 핵심 UX/승인 버그 수정</t>
+        </is>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>09fe10d</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 fix: MES 명칭 정리와 현장 UX 잔여 보완</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B202" s="16" t="inlineStr">
+        <is>
+          <t>15d9c51</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor: X-Ray → DEXCOWIN 시스템명 교체 + MES 용어 정리 + 데스크톱 UX 개선</t>
+        </is>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>f401033</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>merge: fix/mes-terminology-field-ux-pass2 → main</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B204" s="16" t="inlineStr">
+        <is>
+          <t>f7aaa95</t>
+        </is>
+      </c>
+      <c r="C204" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 desktop: 패널 슬라이드 애니메이션 GPU 가속 + 입출고 UX 개선</t>
+        </is>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>aa117be</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 feat: BOM 관리 화면을 단계형 작업 흐름으로 정리</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B206" s="16" t="inlineStr">
+        <is>
+          <t>c1578b0</t>
+        </is>
+      </c>
+      <c r="C206" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 fix: 로그인 화면 부서 색상화 + BOM 상위 품목 더보기</t>
+        </is>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>d75bae5</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 desktop: 로그인 화면 단계별 UI 정리 + 로그인 후 대시보드 강제 진입</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B208" s="16" t="inlineStr">
+        <is>
+          <t>d8fdee8</t>
+        </is>
+      </c>
+      <c r="C208" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 docs: 생산부 재고 매칭 작업 정리본 추가</t>
+        </is>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>698de34</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 fix: lint 오류 수정 (unescaped apostrophe)</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
+          <t>021a224</t>
+        </is>
+      </c>
+      <c r="C210" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor(WIP): category 제거 진행 — 백엔드 코어 정리</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>2c41254</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor: category 제거 및 process_type_code 기준 백엔드 정리</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="inlineStr">
+        <is>
+          <t>b02ed2b</t>
+        </is>
+      </c>
+      <c r="C212" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor: 프론트 품목 분류를 process_type_code 기준으로 정리</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>9634305</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29 refactor: DB 재생성(722건) + process_type_code 문서 단일화</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/개발현황.xlsx
+++ b/data/개발현황.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>212건</t>
+          <t>226건</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>23 / 33개 (70%)</t>
+          <t>27 / 36개 (75%)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30  ■  (2)</t>
+          <t>2026-04-30  ■■■■■■■■  (16)</t>
         </is>
       </c>
     </row>
@@ -988,13 +988,14 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>창고 승인 기반 입출고 흐름·직원별 장바구니
-작업자 PIN 로그인·감사 이력
-시스템명 MES 통일·품목 분류 개편(진행 중)</t>
+          <t>창고 승인 흐름·장바구니·PIN 로그인
+입출고탭 개편(부서필터·반품·자가승인)
+BOM 플래너·부서 관리 UX 개선
+품목 분류 개편 완료(DB 722건)</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1550,96 +1551,92 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>품목 분류 개편 (process_type_code)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>재고</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>DB 722건 재구성 완료</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="n">
+      <c r="A26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>생산 / 분해 / 반품 처리 Queue</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr"/>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>BOM 플래너 (위저드·일괄 다운로드)</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>QR · 바코드 스캔 완성</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>입출고</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>모바일 카메라 연동</t>
-        </is>
-      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>입출고 부서별 필터·반품·자가승인</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n">
+      <c r="A28" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>실제 운영 데이터 입력</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>권동환 사원 협의 후</t>
-        </is>
-      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>부서 관리 (DnD·컬러 피커·직원 검색)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n">
@@ -1647,12 +1644,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>로그인 및 권한 관리</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -1660,11 +1657,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>화면 구현 완료 — 인증 연동 예정</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n">
@@ -1672,12 +1665,12 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>생산 / 분해 / 반품 처리 Queue</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -1685,11 +1678,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>PC 또는 NAS 서버</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n">
@@ -1697,12 +1686,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>QR · 바코드 스캔 완성</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -1710,7 +1699,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr"/>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>모바일 카메라 연동</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
@@ -1718,12 +1711,12 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>실제 운영 데이터 입력</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
@@ -1731,7 +1724,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr"/>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>권동환 사원 협의 후</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n">
@@ -1739,12 +1736,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>부서별 진행현황 화면</t>
+          <t>로그인 및 권한 관리</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -1754,7 +1751,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>화면 구현 완료 — 인증 연동 예정</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1761,12 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>품목 분류 개편 (process_type_code)</t>
+          <t>외부 접근 환경 구성</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -1779,7 +1776,74 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>PC 또는 NAS 서버</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>부서별 진행현황 화면</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2294,15 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
           <t>2026-04-29 refactor: 프론트 품목 분류를 process_type_code 기준으로 정리
-2026-04-29 refactor: DB 재생성(722건) + process_type_code 문서 단일화</t>
+2026-04-29 refactor: DB 재생성(722건) + process_type_code 문서 단일화
+2026-04-30 admin: 관리자 탭 UX 4종 개선
+fix: stock_requests _bucket_label dept.value → str 직접 참조
+2026-04-30 fix: 재고 목록 spec 미입력 품목 대시 제거</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2255,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D213"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6950,6 +7017,314 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B214" s="16" t="inlineStr">
+        <is>
+          <t>0439f97</t>
+        </is>
+      </c>
+      <c r="C214" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 admin: 관리자 탭 UX 4종 개선</t>
+        </is>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>e5b685d</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>fix: stock_requests _bucket_label dept.value → str 직접 참조</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B216" s="16" t="inlineStr">
+        <is>
+          <t>06763a8</t>
+        </is>
+      </c>
+      <c r="C216" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 fix: 재고 목록 spec 미입력 품목 대시 제거</t>
+        </is>
+      </c>
+      <c r="D216" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>81b1271</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 refactor: process_type suffix 레이블 변경 (조립체→중간공정, F타입→공정완료)</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B218" s="16" t="inlineStr">
+        <is>
+          <t>d4052d9</t>
+        </is>
+      </c>
+      <c r="C218" s="17" t="inlineStr">
+        <is>
+          <t>docs: 주간보고 MES 용어 교체 + 개발현황 04-30 기준 업데이트</t>
+        </is>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>948b49f</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 refactor: 상태 메시지를 이벤트 중심으로 정리</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B220" s="16" t="inlineStr">
+        <is>
+          <t>583e81e</t>
+        </is>
+      </c>
+      <c r="C220" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 admin: 부서 관리 DnD 순서 변경 + 관리 요약 통합 + 색상 팔레트</t>
+        </is>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>ccd838a</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 scripts: ERP 코드 복원 스크립트 + BOM 플래너·재고 매칭 정리본 출력물</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="inlineStr">
+        <is>
+          <t>8a46364</t>
+        </is>
+      </c>
+      <c r="C222" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 admin: 부서 색상 선택 — 스와치 팔레트 → 네이티브 컬러 피커</t>
+        </is>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>8727177</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>Add deploy-ready BOM planner</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B224" s="16" t="inlineStr">
+        <is>
+          <t>12a6e1a</t>
+        </is>
+      </c>
+      <c r="C224" s="17" t="inlineStr">
+        <is>
+          <t>merge: refactor/category-to-process-type-code → main (category 제거 + process_type_code 단일화 + DB 722건 재구성)</t>
+        </is>
+      </c>
+      <c r="D224" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>141ec30</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 backend+desktop+mobile: 입출고탭 개편 — 부서별 작업유형 필터·반품 통합·자가승인</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>e900ec6</t>
+        </is>
+      </c>
+      <c r="C226" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 scripts: BOM 플래너 전면 재설계 — 탭 화면 + 위저드 + 일괄 다운로드</t>
+        </is>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>492effb</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 refactor: 부서 색 단일 소스화(DepartmentsContext) + 관리자 직원 검색</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/개발현황.xlsx
+++ b/data/개발현황.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 04-30 (21일)</t>
+          <t>2026-04-10 ~ 04-30 (21일 · 근무일 15일)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>226건</t>
+          <t>229건</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>27 / 36개 (75%)</t>
+          <t>35 / 42개 (83%)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30  ■■■■■■■■  (16)</t>
+          <t>2026-04-30  ■■■■■■■■■  (19)</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>ERP 자재 코드 체계 통일</t>
+          <t>자재 코드 체계 통일</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>BOM 등록 / 조회</t>
+          <t>품목 분류 개편 (process_type_code)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1221,7 +1221,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>DB 722건 재구성</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>BOM 웹 수정 기능</t>
+          <t>재고 실사 (Physical Count)</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1242,7 +1246,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>강제 조정 포함</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -1250,12 +1258,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>BOM Where-Used 조회</t>
+          <t>차이 분석 (Variance)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1263,7 +1271,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>실제-예상 수량 차이 기록</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -1271,12 +1283,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>직원 명단 관리</t>
+          <t>폐기 · 분실 이력 관리</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1284,7 +1296,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Scrap / Loss 라우터</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -1292,12 +1308,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>부서별 담당 색상 배지 표시</t>
+          <t>입출고 단계형 Wizard UX</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>직원</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1313,12 +1329,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>관리자 화면</t>
+          <t>입출고 부서별 필터 · 반품 · 자가승인</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1334,12 +1350,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>데이터 CSV 내보내기</t>
+          <t>창고 승인 기반 입출고 흐름</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1347,7 +1363,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>요청→승인→처리</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1355,12 +1375,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PC 화면 (데스크톱)</t>
+          <t>직원별 저장형 입출고 장바구니</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1368,7 +1388,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>화면 이탈 후 유지</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -1376,12 +1400,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>모바일 화면</t>
+          <t>생산 / 분해 / 반품 처리 Queue</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1389,7 +1413,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>2단계 워크플로</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1397,12 +1425,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>다크 / 라이트 모드</t>
+          <t>QR · 바코드 스캔</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>입출고</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1410,7 +1438,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>BarcodeDetector + zxing</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -1418,12 +1450,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>입출고 단계형 Wizard UX</t>
+          <t>출하 패키지 관리</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>출하</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1431,7 +1463,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>묶음 CRUD + 품목 관리</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -1439,12 +1475,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>원클릭 실행 (start.bat)</t>
+          <t>BOM 등록 / 조회</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1460,12 +1496,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>테스트 자동화 (CI)</t>
+          <t>BOM 웹 수정 기능</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1481,12 +1517,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>창고 승인 기반 입출고 흐름</t>
+          <t>BOM Where-Used 조회</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -1494,11 +1530,7 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>요청→승인→처리 단계 분리</t>
-        </is>
-      </c>
+      <c r="E22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -1506,12 +1538,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>직원별 저장형 입출고 장바구니</t>
+          <t>BOM 플래너 (위저드 · 일괄 다운로드)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1519,11 +1551,7 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>화면 이탈 후에도 작업 유지</t>
-        </is>
-      </c>
+      <c r="E23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -1531,12 +1559,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>작업자 PIN 로그인 + 감사 이력</t>
+          <t>직원 명단 관리</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -1544,11 +1572,7 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>수정 이력 자동 기록</t>
-        </is>
-      </c>
+      <c r="E24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -1556,12 +1580,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>품목 분류 개편 (process_type_code)</t>
+          <t>부서별 담당 색상 배지 표시</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>직원</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1569,11 +1593,7 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>DB 722건 재구성 완료</t>
-        </is>
-      </c>
+      <c r="E25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -1581,12 +1601,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BOM 플래너 (위저드·일괄 다운로드)</t>
+          <t>작업자 PIN 로그인 + 감사 이력</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -1594,7 +1614,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>수정 이력 자동 기록</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -1602,12 +1626,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>입출고 부서별 필터·반품·자가승인</t>
+          <t>로그인 및 권한 관리</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1615,7 +1639,11 @@
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>PIN 기반 — 역할별 접근 제어 예정</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -1623,204 +1651,196 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>부서 관리 (DnD·컬러 피커·직원 검색)</t>
+          <t>PC 화면 (데스크톱)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>모바일 화면</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>다크 / 라이트 모드</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>관리자 화면</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>✅ 완료</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>생산 / 분해 / 반품 처리 Queue</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>QR · 바코드 스캔 완성</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>입출고</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>모바일 카메라 연동</t>
-        </is>
-      </c>
+      <c r="E31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n">
+      <c r="A32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>실제 운영 데이터 입력</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>권동환 사원 협의 후</t>
-        </is>
-      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>부서 관리 (DnD · 컬러 피커 · 검색)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n">
+      <c r="A33" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>로그인 및 권한 관리</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>화면 구현 완료 — 인증 연동 예정</t>
-        </is>
-      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>데이터 CSV 내보내기</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n">
+      <c r="A34" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>외부 접근 환경 구성</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>원클릭 실행 (start.bat)</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>PC 또는 NAS 서버</t>
-        </is>
-      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n">
+      <c r="A35" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>발주 관리</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr"/>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>테스트 자동화 (CI)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>pytest 42건 + vitest 12건</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n">
+      <c r="A36" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>생산 실적 / 원가 관리</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>WAL-safe 백업 / 복구</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>ops 스크립트 자동화</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
@@ -1828,22 +1848,164 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>부서별 진행현황 화면</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>실제 운영 데이터 입력</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>권동환 사원 협의 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>출하 거래처 관리</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>출하</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>거래처 마스터 + 출하 이력</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2456,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -2307,7 +2469,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4901,7 +5063,7 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -4923,7 +5085,7 @@
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -4945,7 +5107,7 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5151,7 @@
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5173,7 @@
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5195,7 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5217,7 @@
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5239,7 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5261,7 @@
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5283,7 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5305,7 @@
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5327,7 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5393,7 @@
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5415,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>devx</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5459,7 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5481,7 @@
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>devx</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5503,7 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5525,7 @@
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5547,7 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5569,7 @@
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5591,7 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5613,7 @@
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5635,7 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5657,7 @@
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5679,7 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5701,7 @@
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5723,7 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5745,7 @@
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5767,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5789,7 @@
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5811,7 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5833,7 @@
       </c>
       <c r="D152" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5855,7 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5877,7 @@
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5899,7 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5921,7 @@
       </c>
       <c r="D156" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5943,7 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5965,7 @@
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5987,7 @@
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5847,7 +6009,7 @@
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -5869,7 +6031,7 @@
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5891,7 +6053,7 @@
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5913,7 +6075,7 @@
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>backend</t>
         </is>
       </c>
     </row>
@@ -5935,7 +6097,7 @@
       </c>
       <c r="D164" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>frontend</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6141,7 @@
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6163,7 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6185,7 @@
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6207,7 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6229,7 @@
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6251,7 @@
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6273,7 @@
       </c>
       <c r="D172" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6295,7 @@
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6317,7 @@
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6339,7 @@
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6361,7 @@
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6383,7 @@
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6427,7 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6449,7 @@
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6471,7 @@
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6493,7 @@
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6515,7 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6537,7 @@
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6559,7 @@
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6581,7 @@
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6603,7 @@
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6625,7 @@
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6647,7 @@
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6669,7 @@
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6691,7 @@
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6713,7 @@
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6735,7 @@
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6757,7 @@
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6779,7 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>merge</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6801,7 @@
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6823,7 @@
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6845,7 @@
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>merge</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6867,7 @@
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6889,7 @@
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6911,7 @@
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6933,7 @@
       </c>
       <c r="D202" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6955,7 @@
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>merge</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6977,7 @@
       </c>
       <c r="D204" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6999,7 @@
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>feat</t>
         </is>
       </c>
     </row>
@@ -6859,7 +7021,7 @@
       </c>
       <c r="D206" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6881,7 +7043,7 @@
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -6903,7 +7065,7 @@
       </c>
       <c r="D208" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -6925,7 +7087,7 @@
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -6947,7 +7109,7 @@
       </c>
       <c r="D210" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6969,7 +7131,7 @@
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7153,7 @@
       </c>
       <c r="D212" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7175,7 @@
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7197,7 @@
       </c>
       <c r="D214" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7241,7 @@
       </c>
       <c r="D216" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>fix</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7263,7 @@
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7307,7 @@
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7329,7 @@
       </c>
       <c r="D220" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7351,7 @@
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>scripts</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7373,7 @@
       </c>
       <c r="D222" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7417,7 @@
       </c>
       <c r="D224" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>merge</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7461,7 @@
       </c>
       <c r="D226" s="16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>scripts</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7483,73 @@
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>refactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B228" s="16" t="inlineStr">
+        <is>
+          <t>16c2466</t>
+        </is>
+      </c>
+      <c r="C228" s="17" t="inlineStr">
+        <is>
+          <t>docs: 주간보고·개발현황 main 브랜치 04-30 반영</t>
+        </is>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>2ee458c</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-30 fix: 운영 위험 5종 정리 (PIN 해시화·/reset 통일·category 잔재 제거)</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B230" s="16" t="inlineStr">
+        <is>
+          <t>d744e21</t>
+        </is>
+      </c>
+      <c r="C230" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-30 merge: feat/operational-cleanup → main (운영 위험 5종 정리)</t>
+        </is>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>merge</t>
         </is>
       </c>
     </row>

--- a/data/개발현황.xlsx
+++ b/data/개발현황.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>229건</t>
+          <t>230건</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30  ■■■■■■■■■  (19)</t>
+          <t>2026-04-30  ■■■■■■■■■■  (20)</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7553,6 +7553,28 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>c15fcd4</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>docs: 개발현황 엑셀 3종 개선</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
